--- a/public/exports-from-60/29189595.xlsx
+++ b/public/exports-from-60/29189595.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027738</t>
+          <t xml:space="preserve">200027739</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -13564,7 +13564,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">

--- a/public/exports-from-60/29189595.xlsx
+++ b/public/exports-from-60/29189595.xlsx
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027739</t>
+          <t xml:space="preserve">200027738</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">

--- a/public/exports-from-60/29189595.xlsx
+++ b/public/exports-from-60/29189595.xlsx
@@ -13564,7 +13564,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -14464,7 +14464,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -17741,30 +17741,30 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 11</t>
+          <t xml:space="preserve">Biotekparken 1</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100046682</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J237">
-        <v>5120</v>
+        <v>798</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558253</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,30 +17816,30 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 13</t>
+          <t xml:space="preserve">Biotekparken 1</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100046682</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J238">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558254</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,30 +17891,30 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 23</t>
+          <t xml:space="preserve">Elise Sørensens Vej 2</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">1352997</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J239">
-        <v>431</v>
+        <v>1771</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558244</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,30 +17966,30 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 23</t>
+          <t xml:space="preserve">Elledevej 59</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">2459947</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J240">
-        <v>3294</v>
+        <v>2103</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558263</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,30 +18041,30 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Rynkevangen 14C</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">5342669</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J241">
-        <v>1326</v>
+        <v>980</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558264</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,30 +18116,30 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Torvet 3</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">5341684</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J242">
-        <v>408</v>
+        <v>1510</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558248</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Hyldens Kvarter 5</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18201,30 +18201,30 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100430394</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J243">
-        <v>754</v>
+        <v>240</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311562887</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 27</t>
+          <t xml:space="preserve">Hyldens Kvarter 9</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18276,30 +18276,30 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100430394, 100562924</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J244">
-        <v>341</v>
+        <v>593</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311562885</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotekparken 1</t>
+          <t xml:space="preserve">Klostermosen 2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,30 +18351,30 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046682</t>
+          <t xml:space="preserve">275985</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J245">
-        <v>798</v>
+        <v>414</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558253</t>
+          <t xml:space="preserve">311586360</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,40 +18416,40 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotekparken 1</t>
+          <t xml:space="preserve">Centret 9</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4470</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046682</t>
+          <t xml:space="preserve">9921582</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J246">
-        <v>683</v>
+        <v>633</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558254</t>
+          <t xml:space="preserve">311594043</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,17 +18491,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elise Sørensens Vej 2</t>
+          <t xml:space="preserve">Odinsvej 20</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352997</t>
+          <t xml:space="preserve">2472174</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,21 +18510,21 @@
         </is>
       </c>
       <c r="J247">
-        <v>1771</v>
+        <v>2864</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558244</t>
+          <t xml:space="preserve">311617056</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-07-26</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledevej 59</t>
+          <t xml:space="preserve">Bredgade 26</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18576,30 +18576,30 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459947</t>
+          <t xml:space="preserve">5341470</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J248">
-        <v>2103</v>
+        <v>1011</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558263</t>
+          <t xml:space="preserve">311620368</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rynkevangen 14C</t>
+          <t xml:space="preserve">Elledevej 63</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,30 +18651,30 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5342669</t>
+          <t xml:space="preserve">2459948</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J249">
-        <v>980</v>
+        <v>94</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558264</t>
+          <t xml:space="preserve">311620365</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 3</t>
+          <t xml:space="preserve">Melbygade 2B</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5341684</t>
+          <t xml:space="preserve">2459072</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -18735,21 +18735,21 @@
         </is>
       </c>
       <c r="J250">
-        <v>1510</v>
+        <v>308</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558248</t>
+          <t xml:space="preserve">311620364</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,40 +18791,40 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 5</t>
+          <t xml:space="preserve">Havnepladsen 1</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4591</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430394</t>
+          <t xml:space="preserve">2454631</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J251">
-        <v>240</v>
+        <v>69</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562887</t>
+          <t xml:space="preserve">311620788</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,40 +18866,40 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 9</t>
+          <t xml:space="preserve">Havnepladsen 1</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4591</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430394, 100562924</t>
+          <t xml:space="preserve">2454631</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J252">
-        <v>593</v>
+        <v>65</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562885</t>
+          <t xml:space="preserve">311620787</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,40 +18941,40 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 2</t>
+          <t xml:space="preserve">Havnevej 11D</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4591</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">275985</t>
+          <t xml:space="preserve">2454631</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J253">
-        <v>414</v>
+        <v>200</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586360</t>
+          <t xml:space="preserve">311620790</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,40 +19016,40 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centret 9</t>
+          <t xml:space="preserve">Radiovej 1</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">4470</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">9921582</t>
+          <t xml:space="preserve">9416235</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J254">
-        <v>633</v>
+        <v>252</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594043</t>
+          <t xml:space="preserve">311620792</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-21</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,40 +19091,40 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 20</t>
+          <t xml:space="preserve">Radiovej 5</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2472174</t>
+          <t xml:space="preserve">9416235</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J255">
-        <v>2864</v>
+        <v>486</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311617056</t>
+          <t xml:space="preserve">311620791</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-26</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,17 +19166,17 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 26</t>
+          <t xml:space="preserve">Algade 14</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4281</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5341470</t>
+          <t xml:space="preserve">2474884</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -19185,11 +19185,11 @@
         </is>
       </c>
       <c r="J256">
-        <v>1011</v>
+        <v>357</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620368</t>
+          <t xml:space="preserve">311622694</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledevej 63</t>
+          <t xml:space="preserve">Langagervej 15</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459948</t>
+          <t xml:space="preserve">5343581</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -19260,11 +19260,11 @@
         </is>
       </c>
       <c r="J257">
-        <v>94</v>
+        <v>653</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620365</t>
+          <t xml:space="preserve">311622692</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,30 +19316,30 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbygade 2B</t>
+          <t xml:space="preserve">Omfartsvejen 5</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4281</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459072</t>
+          <t xml:space="preserve">7544797</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J258">
-        <v>308</v>
+        <v>403</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620364</t>
+          <t xml:space="preserve">311622697</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,30 +19391,30 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepladsen 1</t>
+          <t xml:space="preserve">Røsnæsvej 225</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">4591</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2454631</t>
+          <t xml:space="preserve">7761346</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J259">
-        <v>69</v>
+        <v>350</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620788</t>
+          <t xml:space="preserve">311622695</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,30 +19466,30 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepladsen 1</t>
+          <t xml:space="preserve">Græsmarken 19B</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4591</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2454631</t>
+          <t xml:space="preserve">8316898</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>65</v>
+        <v>362</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620787</t>
+          <t xml:space="preserve">311629060</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,30 +19541,30 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 11D</t>
+          <t xml:space="preserve">Stadion Alle 13</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">4591</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2454631</t>
+          <t xml:space="preserve">8116851</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J261">
-        <v>200</v>
+        <v>709</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620790</t>
+          <t xml:space="preserve">311629056</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiovej 1</t>
+          <t xml:space="preserve">Røsnæsvej 69B</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19626,30 +19626,30 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416235</t>
+          <t xml:space="preserve">276423</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J262">
-        <v>252</v>
+        <v>1452</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620792</t>
+          <t xml:space="preserve">311677823</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2033-05-02</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiovej 5</t>
+          <t xml:space="preserve">Frederik Andersensvej 1</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19701,30 +19701,30 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416235</t>
+          <t xml:space="preserve">5342092</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J263">
-        <v>486</v>
+        <v>395</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620791</t>
+          <t xml:space="preserve">311803915</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2034-12-20</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,40 +19766,40 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 14</t>
+          <t xml:space="preserve">Rosenvænget 11</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2474884</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J264">
-        <v>357</v>
+        <v>5120</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622694</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,40 +19841,40 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langagervej 15</t>
+          <t xml:space="preserve">Rosenvænget 13</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5343581</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J265">
-        <v>653</v>
+        <v>682</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622692</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,40 +19916,40 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omfartsvejen 5</t>
+          <t xml:space="preserve">Rosenvænget 23</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">7544797</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J266">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622697</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,40 +19991,40 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 225</t>
+          <t xml:space="preserve">Rosenvænget 23</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">7761346</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J267">
-        <v>350</v>
+        <v>3294</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622695</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,40 +20066,40 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græsmarken 19B</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316898</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J268">
-        <v>362</v>
+        <v>1326</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629060</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,40 +20141,40 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 13</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116851</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J269">
-        <v>709</v>
+        <v>408</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629056</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,40 +20216,40 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 69B</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">276423</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J270">
-        <v>1452</v>
+        <v>754</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677823</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-02</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,40 +20291,40 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Andersensvej 1</t>
+          <t xml:space="preserve">Rosenvænget 27</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5342092</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J271">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803915</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-20</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
